--- a/Data/Enemy/EnemyPatrolPos.xlsx
+++ b/Data/Enemy/EnemyPatrolPos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\Game\DXLibProject_Sample\DXLibProject_Sample\Data\Enemy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\Game\3DGame\Data\Enemy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C65D41B-7E53-441D-A083-00396E3014AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D10C0B-D059-40BE-8FCB-3DA696C8BF19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2160" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="450" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -372,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
@@ -474,7 +474,7 @@
         <v>200</v>
       </c>
       <c r="D6">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>200</v>
@@ -491,9 +491,60 @@
         <v>300</v>
       </c>
       <c r="D7">
+        <v>100</v>
+      </c>
+      <c r="E7">
         <v>300</v>
       </c>
-      <c r="E7">
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>500</v>
+      </c>
+      <c r="D8">
+        <v>100</v>
+      </c>
+      <c r="E8">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>400</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
+      </c>
+      <c r="E9">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>300</v>
+      </c>
+      <c r="D10">
+        <v>100</v>
+      </c>
+      <c r="E10">
         <v>300</v>
       </c>
     </row>

--- a/Data/Enemy/EnemyPatrolPos.xlsx
+++ b/Data/Enemy/EnemyPatrolPos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\Game\3DGame\Data\Enemy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D10C0B-D059-40BE-8FCB-3DA696C8BF19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4044C6CA-B7DE-4FFF-8B5B-C307E34F8C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="450" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -406,7 +406,7 @@
         <v>100</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E2">
         <v>100</v>
@@ -423,7 +423,7 @@
         <v>200</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E3">
         <v>200</v>
@@ -440,7 +440,7 @@
         <v>300</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E4">
         <v>300</v>
@@ -454,10 +454,10 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D5">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E5">
         <v>100</v>
@@ -471,10 +471,10 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="D6">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E6">
         <v>200</v>
@@ -488,10 +488,10 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="D7">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E7">
         <v>300</v>
@@ -508,7 +508,7 @@
         <v>500</v>
       </c>
       <c r="D8">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E8">
         <v>500</v>
@@ -525,7 +525,7 @@
         <v>400</v>
       </c>
       <c r="D9">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E9">
         <v>400</v>
@@ -542,7 +542,7 @@
         <v>300</v>
       </c>
       <c r="D10">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E10">
         <v>300</v>

--- a/Data/Enemy/EnemyPatrolPos.xlsx
+++ b/Data/Enemy/EnemyPatrolPos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\Game\3DGame\Data\Enemy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4044C6CA-B7DE-4FFF-8B5B-C307E34F8C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D74EC8-7617-4CC9-9B6A-7FFD256EBFD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -372,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
@@ -403,13 +403,13 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D2">
         <v>150</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -420,30 +420,30 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="D3">
         <v>150</v>
       </c>
       <c r="E3">
-        <v>200</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
         <v>0</v>
       </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
       <c r="C4">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="D4">
         <v>150</v>
       </c>
       <c r="E4">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -451,16 +451,16 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="D5">
         <v>150</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -468,33 +468,33 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="D6">
         <v>150</v>
       </c>
       <c r="E6">
-        <v>200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="D7">
         <v>150</v>
       </c>
       <c r="E7">
-        <v>300</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -502,16 +502,16 @@
         <v>2</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="D8">
         <v>150</v>
       </c>
       <c r="E8">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -519,32 +519,15 @@
         <v>2</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="D9">
         <v>150</v>
       </c>
       <c r="E9">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>2</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10">
-        <v>300</v>
-      </c>
-      <c r="D10">
-        <v>150</v>
-      </c>
-      <c r="E10">
         <v>300</v>
       </c>
     </row>
